--- a/sheets/조재수대금교본/검수/라노비아.xlsx
+++ b/sheets/조재수대금교본/검수/라노비아.xlsx
@@ -4105,8 +4105,7 @@
       <c r="C5" s="23"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="E5" s="23"/>
@@ -4118,29 +4117,25 @@
       <c r="G5" s="23"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="I5" s="23"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="K5" s="23"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">應
-‹</t>
+          <t xml:space="preserve">應</t>
         </is>
       </c>
       <c r="M5" s="23"/>
       <c r="N5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲
-‹</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="O5" s="23"/>
@@ -4282,15 +4277,13 @@
       <c r="C9" s="23"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="E9" s="23"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G9" s="23"/>
@@ -4343,29 +4336,13 @@
         </is>
       </c>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="24"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="24"/>
     </row>
     <row r="11" ht="117.77" customHeight="true">
@@ -4468,15 +4445,13 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="E13" s="23"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="G13" s="23"/>
@@ -4488,22 +4463,19 @@
       <c r="I13" s="23"/>
       <c r="J13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="M13" s="23"/>
       <c r="N13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="O13" s="23"/>
@@ -4530,8 +4502,7 @@
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -4677,18 +4648,13 @@
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D18" s="21"/>
       <c r="E18" s="24"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –
-應
-‹</t>
+應</t>
         </is>
       </c>
       <c r="G18" s="24"/>

--- a/sheets/조재수대금교본/검수/라노비아.xlsx
+++ b/sheets/조재수대금교본/검수/라노비아.xlsx
@@ -3947,26 +3947,26 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="10.71" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="105.26" customHeight="true">
+    <row r="2" ht="81.63" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
       <c r="N2" s="20"/>
       <c r="O2" s="20"/>
     </row>
-    <row r="3" ht="117.77" customHeight="true">
+    <row r="3" ht="91.25" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="O3" s="22"/>
     </row>
-    <row r="4" ht="117.77" customHeight="true">
+    <row r="4" ht="91.25" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="O4" s="23"/>
     </row>
-    <row r="5" ht="117.77" customHeight="true">
+    <row r="5" ht="91.25" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="O5" s="23"/>
     </row>
-    <row r="6" ht="117.77" customHeight="true">
+    <row r="6" ht="91.25" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4197,7 +4197,7 @@
       </c>
       <c r="O6" s="24"/>
     </row>
-    <row r="7" ht="117.77" customHeight="true">
+    <row r="7" ht="91.25" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
       </c>
       <c r="O7" s="22"/>
     </row>
-    <row r="8" ht="117.77" customHeight="true">
+    <row r="8" ht="91.25" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -4271,7 +4271,7 @@
       <c r="N8" s="21"/>
       <c r="O8" s="23"/>
     </row>
-    <row r="9" ht="117.77" customHeight="true">
+    <row r="9" ht="91.25" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="23"/>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="O9" s="23"/>
     </row>
-    <row r="10" ht="117.77" customHeight="true">
+    <row r="10" ht="91.25" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4345,7 +4345,7 @@
       <c r="N10" s="21"/>
       <c r="O10" s="24"/>
     </row>
-    <row r="11" ht="117.77" customHeight="true">
+    <row r="11" ht="91.25" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="O11" s="22"/>
     </row>
-    <row r="12" ht="117.77" customHeight="true">
+    <row r="12" ht="91.25" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="23"/>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="O12" s="23"/>
     </row>
-    <row r="13" ht="117.77" customHeight="true">
+    <row r="13" ht="91.25" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="O13" s="23"/>
     </row>
-    <row r="14" ht="117.77" customHeight="true">
+    <row r="14" ht="91.25" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="O14" s="24"/>
     </row>
-    <row r="15" ht="117.77" customHeight="true">
+    <row r="15" ht="91.25" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="O15" s="22"/>
     </row>
-    <row r="16" ht="117.77" customHeight="true">
+    <row r="16" ht="91.25" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -4607,7 +4607,7 @@
       <c r="N16" s="21"/>
       <c r="O16" s="23"/>
     </row>
-    <row r="17" ht="117.77" customHeight="true">
+    <row r="17" ht="91.25" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="O17" s="23"/>
     </row>
-    <row r="18" ht="117.77" customHeight="true">
+    <row r="18" ht="91.25" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="24"/>
@@ -4697,6 +4697,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="38"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="49"/>
 </worksheet>
 </file>